--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-08.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +866,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -929,6 +947,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,6 +1028,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1087,6 +1109,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1166,6 +1190,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1245,6 +1271,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1324,6 +1352,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1403,6 +1433,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1482,6 +1514,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1561,6 +1595,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1640,6 +1676,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1649,37 +1687,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PSV x Fortuna Sittard</t>
+          <t>Atl. Tucuman x Sarmiento Junin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atl. Tucuman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sarmiento Junin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1688,37 +1726,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>11.63</v>
+        <v>9.09</v>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>8.77</v>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8.77</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1733,22 +1781,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923 x Zemun</t>
+          <t>PSV x Fortuna Sittard</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1767,20 +1815,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="K17" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>11.63</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1798,6 +1846,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1807,27 +1857,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SLOVAKIA 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Spartak Trnava x Dukla Banska Bystrica</t>
+          <t>FK Radnicki 1923 x Zemun</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dukla Banska Bystrica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1846,13 +1896,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="L18" t="n">
-        <v>18.52</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
@@ -1877,6 +1927,8 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1886,37 +1938,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Clermont x Reims</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Clermont</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
+          <t>Radnicki 1923 x Zemun</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1925,37 +1969,45 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="L19" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1965,27 +2017,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Club Football Estrela x Sporting Lisbon</t>
+          <t>Spartak Trnava x Dukla Banska Bystrica</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Football Estrela</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Dukla Banska Bystrica</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2004,20 +2056,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="K20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="L20" t="n">
-        <v>17.24</v>
+        <v>18.52</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2035,6 +2087,8 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2044,37 +2098,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOLIVIA 1</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>The Strongest x Club Independiente Petrolero</t>
+          <t>Clermont x Reims</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Independiente Petrolero</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2083,20 +2137,20 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>13.16</v>
+        <v>4.55</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2114,6 +2168,8 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2123,37 +2179,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Botafogo FR x Fluminense</t>
+          <t>Club Football Estrela x Sporting Lisbon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Club Football Estrela</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2162,20 +2218,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="L22" t="n">
-        <v>6.25</v>
+        <v>17.24</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,6 +2249,8 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2202,29 +2260,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>BOLIVIA 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Radnicki 1923 x Zemun</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>The Strongest x Club Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Club Independiente Petrolero</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2233,42 +2299,297 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="K23" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="L23" t="n">
-        <v>8.699999999999999</v>
+        <v>13.16</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BRAZIL 3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ituano x Barra FC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Barra FC</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>21</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>200</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="T23" t="b">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="W24" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Botafogo FR x Fluminense</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Botafogo FR</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Correct Score (2x2)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>17</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ARGENTINA 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Independiente x Platense</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Platense</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>22</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="M26" t="n">
+        <v>200</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0x1</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="W26" t="n">
+        <v>9.19</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-08.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5x1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5x5</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-08.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
